--- a/hall/resources/sample/allWareHouse.xlsx
+++ b/hall/resources/sample/allWareHouse.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B7353D-3433-40E2-BC8E-8C558EA9E1FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04B1847-56E8-4A7C-86C6-C408F62EC500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/hall/resources/sample/allWareHouse.xlsx
+++ b/hall/resources/sample/allWareHouse.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project\hall\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04B1847-56E8-4A7C-86C6-C408F62EC500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BCD580-7A24-469A-BCC1-67C441927D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7080" yWindow="1500" windowWidth="21600" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AllWareHouseConfig" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>sid</t>
   </si>
@@ -166,6 +166,10 @@
   </si>
   <si>
     <t>wareId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>String</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -242,7 +246,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -263,6 +267,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -751,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="5" max="6" width="16" customWidth="1"/>
@@ -787,7 +794,9 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
@@ -834,80 +843,90 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>100100</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>50000000</v>
-      </c>
-      <c r="F4">
-        <v>500000</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
+      <c r="A4" s="7"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>100100</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>500000000</v>
+        <v>50000000</v>
       </c>
       <c r="F5">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>100100</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>500000000</v>
+      </c>
+      <c r="F6">
+        <v>5000000</v>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A7">
         <v>3</v>
       </c>
-      <c r="E6">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>100100</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
         <v>5000000000</v>
       </c>
-      <c r="F6">
+      <c r="F7">
         <v>50000000</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>100</v>
       </c>
-      <c r="H6">
+      <c r="H7">
         <v>5000000</v>
       </c>
     </row>

--- a/hall/resources/sample/allWareHouse.xlsx
+++ b/hall/resources/sample/allWareHouse.xlsx
@@ -5,25 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project\hall\resources\sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BCD580-7A24-469A-BCC1-67C441927D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9515FF1-4957-4F1B-9EB9-0800740F98BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="1500" windowWidth="21600" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34320" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AllWareHouseConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="AllWareHouse" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -246,7 +238,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -267,9 +259,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -843,7 +832,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" s="7"/>
+      <c r="A4" s="2"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
